--- a/advertising and peckaging 400.xlsx
+++ b/advertising and peckaging 400.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAZER\Desktop\Rockson project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RAZER\Desktop\Rockson project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17FA4BEF-2889-4CD1-8A65-08651C1126EC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1757039B-B277-45E4-8804-B2F993FF6065}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7290" xr2:uid="{3B03C9F4-DDA8-4A77-879C-FB0FCD35CEB3}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16680" windowHeight="7290" xr2:uid="{3B03C9F4-DDA8-4A77-879C-FB0FCD35CEB3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
